--- a/apps/api/data/CarbonCo_Finance_DPP_v1_3.xlsx
+++ b/apps/api/data/CarbonCo_Finance_DPP_v1_3.xlsx
@@ -16,8 +16,38 @@
     <sheet name="SFDR_Report" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="_Ref_Secteurs" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Controles_QC" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="_Manifest" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="CC_FIN_Raison_Sociale">'Liaison_Donnees'!$C$7</definedName>
+    <definedName name="CC_FIN_Annee_Reporting">'Liaison_Donnees'!$C$8</definedName>
+    <definedName name="CC_FIN_CA_Net">'Liaison_Donnees'!$C$9</definedName>
+    <definedName name="CC_FIN_ETP">'Liaison_Donnees'!$C$10</definedName>
+    <definedName name="CC_FIN_Code_NAF">'Liaison_Donnees'!$C$11</definedName>
+    <definedName name="CC_FIN_CapEx_Total">'Liaison_Donnees'!$C$12</definedName>
+    <definedName name="CC_FIN_OpEx_Eligible_Taxo">'Liaison_Donnees'!$C$13</definedName>
+    <definedName name="CC_FIN_Scope1">'Liaison_Donnees'!$C$15</definedName>
+    <definedName name="CC_FIN_Scope2_LB">'Liaison_Donnees'!$C$16</definedName>
+    <definedName name="CC_FIN_Scope2_MB">'Liaison_Donnees'!$C$17</definedName>
+    <definedName name="CC_FIN_Scope3">'Liaison_Donnees'!$C$18</definedName>
+    <definedName name="CC_FIN_Total_GES">'Liaison_Donnees'!$C$19</definedName>
+    <definedName name="CC_FIN_Intensite_CA">'Liaison_Donnees'!$C$20</definedName>
+    <definedName name="CC_FIN_Part_Scope3">'Liaison_Donnees'!$C$21</definedName>
+    <definedName name="CC_FIN_Part_ENR">'Liaison_Donnees'!$C$23</definedName>
+    <definedName name="CC_FIN_Taxo_CA_Aligne">'Liaison_Donnees'!$C$24</definedName>
+    <definedName name="CC_FIN_Taxo_CapEx_Aligne">'Liaison_Donnees'!$C$25</definedName>
+    <definedName name="CC_FIN_CBAM_Cout">'Liaison_Donnees'!$C$26</definedName>
+    <definedName name="CC_FIN_SBTI_Taux_S12">'Liaison_Donnees'!$C$28</definedName>
+    <definedName name="CC_FIN_SBTI_Baseline_S12">'Liaison_Donnees'!$C$29</definedName>
+    <definedName name="CC_FIN_SBTI_Annee_Baseline">'Liaison_Donnees'!$C$30</definedName>
+    <definedName name="CC_FIN_Prix_ETS">'Finance_Climat'!$D$7</definedName>
+    <definedName name="CC_FIN_Quota_ETS">'Finance_Climat'!$D$9</definedName>
+    <definedName name="CC_FIN_CAGR_Prix_Carbone">'Finance_Climat'!$D$15</definedName>
+    <definedName name="CC_FIN_Exposition_Totale">'Finance_Climat'!$D$12</definedName>
+    <definedName name="CC_FIN_CapEx_Decarb_S12">'Finance_Climat'!$D$46</definedName>
+    <definedName name="CC_FIN_CapEx_Decarb_S3">'Finance_Climat'!$D$47</definedName>
+    <definedName name="CC_FIN_Green_CapEx_Pct">'Finance_Climat'!$D$50</definedName>
+  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -4472,6 +4502,87 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>CarbonCo_Finance_DPP_v1_3 — Manifest</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Onglets obligatoires</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Couverture,Sommaire,Liaison_Donnees,Finance_Climat,DPP_Produits,SFDR_Report,Benchmark,Controles_QC,Claude Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Plages CC_* requises</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Controles QC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7620,10 +7731,10 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A5:J5"/>
     <mergeCell ref="A16:J16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A3:J3"/>
